--- a/research/traditional_assets/database/data/sweden/sweden_utility_water.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_utility_water.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-4.281990521327014</v>
+        <v>-7.383838383838383</v>
       </c>
       <c r="H2">
-        <v>-4.739336492890995</v>
+        <v>-8.232323232323232</v>
       </c>
       <c r="I2">
-        <v>-4.71563981042654</v>
+        <v>-8.080808080808081</v>
       </c>
       <c r="J2">
-        <v>-4.71563981042654</v>
+        <v>-8.080808080808081</v>
       </c>
       <c r="K2">
-        <v>-1.99</v>
+        <v>-1.6</v>
       </c>
       <c r="L2">
-        <v>-4.71563981042654</v>
+        <v>-8.080808080808081</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,31 +627,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>0.3266787658802178</v>
+        <v>0.2838801711840228</v>
       </c>
       <c r="W2">
-        <v>-0.8540772532188841</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="X2">
-        <v>0.03568534419585297</v>
+        <v>0.06773506484371264</v>
       </c>
       <c r="Y2">
-        <v>-0.8897625974147371</v>
+        <v>-0.6010683981770459</v>
       </c>
       <c r="Z2">
-        <v>0.2682771773680865</v>
+        <v>0.165</v>
       </c>
       <c r="AA2">
-        <v>-1.265098537825811</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AB2">
-        <v>0.03568534419585297</v>
+        <v>0.06773506484371264</v>
       </c>
       <c r="AC2">
-        <v>-1.300783882021664</v>
+        <v>-1.401068398177046</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.8</v>
+        <v>-1.99</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.4851752021563343</v>
+        <v>-0.3964143426294821</v>
       </c>
       <c r="AK2">
-        <v>-1.5</v>
+        <v>-2.726027397260273</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>1.139240506329114</v>
+        <v>1.507575757575758</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-4.281990521327014</v>
+        <v>-7.383838383838383</v>
       </c>
       <c r="H3">
-        <v>-4.739336492890995</v>
+        <v>-8.232323232323232</v>
       </c>
       <c r="I3">
-        <v>-4.71563981042654</v>
+        <v>-8.080808080808081</v>
       </c>
       <c r="J3">
-        <v>-4.71563981042654</v>
+        <v>-8.080808080808081</v>
       </c>
       <c r="K3">
-        <v>-1.99</v>
+        <v>-1.6</v>
       </c>
       <c r="L3">
-        <v>-4.71563981042654</v>
+        <v>-8.080808080808081</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,31 +746,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="V3">
-        <v>0.3266787658802178</v>
+        <v>0.2838801711840228</v>
       </c>
       <c r="W3">
-        <v>-0.8540772532188841</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="X3">
-        <v>0.03568534419585297</v>
+        <v>0.06773506484371264</v>
       </c>
       <c r="Y3">
-        <v>-0.8897625974147371</v>
+        <v>-0.6010683981770459</v>
       </c>
       <c r="Z3">
-        <v>0.2682771773680865</v>
+        <v>0.165</v>
       </c>
       <c r="AA3">
-        <v>-1.265098537825811</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AB3">
-        <v>0.03568534419585297</v>
+        <v>0.06773506484371264</v>
       </c>
       <c r="AC3">
-        <v>-1.300783882021664</v>
+        <v>-1.401068398177046</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.8</v>
+        <v>-1.99</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.4851752021563343</v>
+        <v>-0.3964143426294821</v>
       </c>
       <c r="AK3">
-        <v>-1.5</v>
+        <v>-2.726027397260273</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>1.139240506329114</v>
+        <v>1.507575757575758</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_utility_water.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_utility_water.xlsx
@@ -587,23 +587,26 @@
           <t>Utility (Water)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0968</v>
+      </c>
       <c r="G2">
-        <v>-7.383838383838383</v>
+        <v>-3.854545454545454</v>
       </c>
       <c r="H2">
-        <v>-8.232323232323232</v>
+        <v>-4.303030303030303</v>
       </c>
       <c r="I2">
-        <v>-8.080808080808081</v>
+        <v>-4.818181818181818</v>
       </c>
       <c r="J2">
-        <v>-8.080808080808081</v>
+        <v>-4.818181818181818</v>
       </c>
       <c r="K2">
-        <v>-1.6</v>
+        <v>-1.67</v>
       </c>
       <c r="L2">
-        <v>-8.080808080808081</v>
+        <v>-5.060606060606061</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,67 +630,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.99</v>
+        <v>0.67</v>
       </c>
       <c r="V2">
-        <v>0.2838801711840228</v>
+        <v>0.162227602905569</v>
       </c>
       <c r="W2">
-        <v>-0.5333333333333333</v>
+        <v>-0.613970588235294</v>
       </c>
       <c r="X2">
-        <v>0.06773506484371264</v>
+        <v>0.05867966206432446</v>
       </c>
       <c r="Y2">
-        <v>-0.6010683981770459</v>
+        <v>-0.6726502502996186</v>
       </c>
       <c r="Z2">
-        <v>0.165</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="AA2">
-        <v>-1.333333333333333</v>
+        <v>-2.178082191780821</v>
       </c>
       <c r="AB2">
-        <v>0.06773506484371264</v>
+        <v>0.05869666092441657</v>
       </c>
       <c r="AC2">
-        <v>-1.401068398177046</v>
+        <v>-2.236778852705238</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AG2">
-        <v>-1.99</v>
+        <v>-0.5750000000000001</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.02248520710059172</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.07883817427385892</v>
       </c>
       <c r="AJ2">
-        <v>-0.3964143426294821</v>
+        <v>-0.1617440225035162</v>
       </c>
       <c r="AK2">
-        <v>-2.726027397260273</v>
+        <v>-1.074766355140187</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-0.06985294117647059</v>
+      </c>
+      <c r="AO2">
+        <v>-318</v>
       </c>
       <c r="AP2">
-        <v>1.507575757575758</v>
+        <v>0.4227941176470588</v>
       </c>
     </row>
     <row r="3">
@@ -706,23 +712,26 @@
           <t>Utility (Water)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0968</v>
+      </c>
       <c r="G3">
-        <v>-7.383838383838383</v>
+        <v>-3.854545454545454</v>
       </c>
       <c r="H3">
-        <v>-8.232323232323232</v>
+        <v>-4.303030303030303</v>
       </c>
       <c r="I3">
-        <v>-8.080808080808081</v>
+        <v>-4.818181818181818</v>
       </c>
       <c r="J3">
-        <v>-8.080808080808081</v>
+        <v>-4.818181818181818</v>
       </c>
       <c r="K3">
-        <v>-1.6</v>
+        <v>-1.67</v>
       </c>
       <c r="L3">
-        <v>-8.080808080808081</v>
+        <v>-5.060606060606061</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,67 +755,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.99</v>
+        <v>0.67</v>
       </c>
       <c r="V3">
-        <v>0.2838801711840228</v>
+        <v>0.162227602905569</v>
       </c>
       <c r="W3">
-        <v>-0.5333333333333333</v>
+        <v>-0.613970588235294</v>
       </c>
       <c r="X3">
-        <v>0.06773506484371264</v>
+        <v>0.05867966206432446</v>
       </c>
       <c r="Y3">
-        <v>-0.6010683981770459</v>
+        <v>-0.6726502502996186</v>
       </c>
       <c r="Z3">
-        <v>0.165</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="AA3">
-        <v>-1.333333333333333</v>
+        <v>-2.178082191780821</v>
       </c>
       <c r="AB3">
-        <v>0.06773506484371264</v>
+        <v>0.05869666092441657</v>
       </c>
       <c r="AC3">
-        <v>-1.401068398177046</v>
+        <v>-2.236778852705238</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AG3">
-        <v>-1.99</v>
+        <v>-0.5750000000000001</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.02248520710059172</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.07883817427385892</v>
       </c>
       <c r="AJ3">
-        <v>-0.3964143426294821</v>
+        <v>-0.1617440225035162</v>
       </c>
       <c r="AK3">
-        <v>-2.726027397260273</v>
+        <v>-1.074766355140187</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-0.06985294117647059</v>
+      </c>
+      <c r="AO3">
+        <v>-318</v>
       </c>
       <c r="AP3">
-        <v>1.507575757575758</v>
+        <v>0.4227941176470588</v>
       </c>
     </row>
   </sheetData>
